--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484033_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484033_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7743</v>
+        <v>4.5981</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1912</v>
+        <v>1.2955</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5831</v>
+        <v>3.3026</v>
       </c>
       <c r="G2" t="n">
         <v>2.171</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6608</v>
+        <v>0.4846</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9297</v>
+        <v>0.0341</v>
       </c>
       <c r="U2" t="n">
-        <v>0.731</v>
+        <v>0.4505</v>
       </c>
       <c r="V2" t="n">
         <v>0.5538999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0802</v>
+        <v>3.0085</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4357</v>
+        <v>0.5604</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6445</v>
+        <v>2.4481</v>
       </c>
       <c r="G3" t="n">
         <v>3.0574</v>
@@ -688,13 +688,13 @@
         <v>2.7774</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0958</v>
+        <v>0.0241</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3797</v>
+        <v>-0.255</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4754</v>
+        <v>0.279</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8663999999999999</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2393</v>
+        <v>1.9993</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7938</v>
+        <v>-0.6691</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0331</v>
+        <v>2.6684</v>
       </c>
       <c r="G4" t="n">
         <v>2.8081</v>
@@ -766,13 +766,13 @@
         <v>2.3806</v>
       </c>
       <c r="S4" t="n">
-        <v>0.607</v>
+        <v>0.367</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2436</v>
+        <v>-0.1189</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8506</v>
+        <v>0.4859</v>
       </c>
       <c r="V4" t="n">
         <v>0.4113</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. SALA MAS</t>
+          <t>M. BENITO MULLERAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3261</v>
+        <v>1.7898</v>
       </c>
       <c r="E5" t="n">
-        <v>2.881</v>
+        <v>0.1412</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.555</v>
+        <v>1.6486</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6317</v>
+        <v>2.7528</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8116</v>
+        <v>3.0896</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4433</v>
+        <v>-0.3368</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5611</v>
+        <v>2.7484</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3884</v>
+        <v>2.8587</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1728</v>
+        <v>-0.1103</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.9294</v>
+        <v>0.0044</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1999</v>
+        <v>0.2309</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7295</v>
+        <v>-0.2266</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>3.1741</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0198</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0056</v>
+        <v>-0.6234</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0142</v>
+        <v>-0.2028</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6745</v>
+        <v>-1.3271</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0962</v>
+        <v>1.4125</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1638</v>
+        <v>2.3679</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0676</v>
+        <v>-0.9554</v>
       </c>
       <c r="G6" t="n">
         <v>0.874</v>
@@ -922,13 +922,13 @@
         <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5713</v>
+        <v>-0.2551</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3741</v>
+        <v>-0.17</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1973</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. BENITO MULLERAT</t>
+          <t>L. SALA MAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4638</v>
+        <v>0.9817</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5957</v>
+        <v>2.677</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0595</v>
+        <v>-1.6952</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7528</v>
+        <v>0.6317</v>
       </c>
       <c r="H7" t="n">
-        <v>3.0896</v>
+        <v>-0.8116</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3368</v>
+        <v>1.4433</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7484</v>
+        <v>3.5611</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8587</v>
+        <v>0.3884</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1103</v>
+        <v>3.1728</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0044</v>
+        <v>-2.9294</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2309</v>
+        <v>-1.1999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2266</v>
+        <v>-1.7295</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1741</v>
+        <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1522</v>
+        <v>-0.3642</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3602</v>
+        <v>-0.2097</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7919</v>
+        <v>-0.1545</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3271</v>
+        <v>-0.6745</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1771</v>
+        <v>0.7842</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4217</v>
+        <v>-1.6848</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2446</v>
+        <v>2.469</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5255</v>
@@ -1078,13 +1078,13 @@
         <v>2.7774</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5111</v>
+        <v>-0.5498</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2356</v>
+        <v>-0.4987</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2756</v>
+        <v>-0.0511</v>
       </c>
       <c r="V8" t="n">
         <v>0.0741</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8893</v>
+        <v>-0.7592</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1687</v>
+        <v>-0.0667</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7205</v>
+        <v>-0.6925</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0554</v>
@@ -1156,13 +1156,13 @@
         <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2307</v>
+        <v>-0.1006</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2494</v>
+        <v>-0.1474</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6417</v>
+        <v>-4.0014</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5316</v>
+        <v>-2.1438</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1101</v>
+        <v>-1.8576</v>
       </c>
       <c r="G10" t="n">
         <v>-2.606</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1627</v>
+        <v>-0.1969</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8106</v>
+        <v>0.1985</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6479</v>
+        <v>-0.3954</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6032</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4486</v>
+        <v>-4.3669</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4149</v>
+        <v>-2.1088</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0337</v>
+        <v>-2.2582</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6422</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3934</v>
+        <v>-0.3118</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4988</v>
+        <v>-0.1927</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1054</v>
+        <v>-0.1191</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8097</v>
@@ -1345,34 +1345,34 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.823200000000001</v>
+        <v>5.446600000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2546999999999993</v>
+        <v>0.3688000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>5.0779</v>
+        <v>5.0778</v>
       </c>
       <c r="G12" t="n">
-        <v>5.465899999999999</v>
+        <v>5.465900000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>6.728600000000001</v>
+        <v>6.728599999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.262900000000001</v>
+        <v>-1.2629</v>
       </c>
       <c r="J12" t="n">
         <v>14.4679</v>
       </c>
       <c r="K12" t="n">
-        <v>9.934199999999999</v>
+        <v>9.934199999999997</v>
       </c>
       <c r="L12" t="n">
-        <v>4.533899999999999</v>
+        <v>4.5339</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.0022</v>
+        <v>-9.002199999999998</v>
       </c>
       <c r="N12" t="n">
         <v>-3.2056</v>
@@ -1381,7 +1381,7 @@
         <v>-5.7967</v>
       </c>
       <c r="P12" t="n">
-        <v>5.9515</v>
+        <v>5.951499999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.8948</v>
@@ -1390,19 +1390,19 @@
         <v>18.8465</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3522</v>
+        <v>-1.7288</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.6067</v>
+        <v>-1.9832</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2541999999999995</v>
+        <v>0.2543</v>
       </c>
       <c r="V12" t="n">
         <v>-4.2416</v>
       </c>
       <c r="W12" t="n">
-        <v>0.7787999999999998</v>
+        <v>0.7787999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-5.0204</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6829</v>
+        <v>6.0833</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4054</v>
+        <v>5.6094</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2775</v>
+        <v>0.4739</v>
       </c>
       <c r="G13" t="n">
         <v>2.3116</v>
@@ -1468,13 +1468,13 @@
         <v>1.7855</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4302</v>
+        <v>-0.0297</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6291</v>
+        <v>-0.425</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1989</v>
+        <v>0.3953</v>
       </c>
       <c r="V13" t="n">
         <v>2.2144</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7487</v>
+        <v>2.3723</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3946</v>
+        <v>1.4364</v>
       </c>
       <c r="F14" t="n">
-        <v>0.354</v>
+        <v>0.9359</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.296</v>
+        <v>1.1158</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2392</v>
+        <v>2.2222</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9432</v>
+        <v>-1.1064</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8877</v>
+        <v>1.4963</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7672</v>
+        <v>1.9355</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1205</v>
+        <v>-0.4392</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1837</v>
+        <v>-0.3805</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0064</v>
+        <v>0.2867</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8227</v>
+        <v>-0.6672</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R14" t="n">
         <v>0.9919</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7788</v>
+        <v>0.6532</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3005</v>
+        <v>0.3288</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4783</v>
+        <v>0.3244</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2739</v>
+        <v>0.6032</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2065</v>
+        <v>0.6032</v>
       </c>
       <c r="X14" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6469</v>
+        <v>2.1824</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5384</v>
+        <v>1.8845</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1085</v>
+        <v>0.2979</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1158</v>
+        <v>-0.296</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2222</v>
+        <v>-1.2392</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1064</v>
+        <v>0.9432</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4963</v>
+        <v>0.8877</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9355</v>
+        <v>0.7672</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4392</v>
+        <v>0.1205</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3805</v>
+        <v>-1.1837</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2867</v>
+        <v>-2.0064</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6672</v>
+        <v>0.8227</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9278</v>
+        <v>0.2126</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4308</v>
+        <v>-0.2096</v>
       </c>
       <c r="U15" t="n">
-        <v>0.497</v>
+        <v>0.4222</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6032</v>
+        <v>1.2739</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1479</v>
+        <v>0.6998</v>
       </c>
       <c r="E16" t="n">
-        <v>1.019</v>
+        <v>0.4068</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1289</v>
+        <v>0.293</v>
       </c>
       <c r="G16" t="n">
         <v>1.6959</v>
@@ -1702,13 +1702,13 @@
         <v>0.5952</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5232</v>
+        <v>0.0751</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6746</v>
+        <v>0.0624</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1514</v>
+        <v>0.0127</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6745</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>J. RIERA MESTRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7248</v>
+        <v>0.2929</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.312</v>
+        <v>-0.2319</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0369</v>
+        <v>0.5248</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6132</v>
+        <v>1.5083</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9928</v>
+        <v>-0.5244</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3796</v>
+        <v>2.0327</v>
       </c>
       <c r="J17" t="n">
-        <v>2.0462</v>
+        <v>1.9559</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2405</v>
+        <v>0.0658</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8058</v>
+        <v>1.8901</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.433</v>
+        <v>-0.4477</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2477</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1853</v>
+        <v>0.1425</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5871</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1741</v>
+        <v>-2.1822</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5871</v>
+        <v>0.7935</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6987</v>
+        <v>0.4393</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5499000000000001</v>
+        <v>-0.0056</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1488</v>
+        <v>0.4449</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>-0.266</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RIERA MESTRE</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0693</v>
+        <v>0.1863</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.538</v>
+        <v>0.4372</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4687</v>
+        <v>-0.2509</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5083</v>
+        <v>-0.651</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5244</v>
+        <v>-0.2519</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0327</v>
+        <v>-0.3991</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9559</v>
+        <v>1.4801</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0658</v>
+        <v>0.9529</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8901</v>
+        <v>0.5272</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.4477</v>
+        <v>-2.1311</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-1.2048</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1425</v>
+        <v>-0.9263</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
         <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0771</v>
+        <v>0.2225</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3117</v>
+        <v>-0.051</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3888</v>
+        <v>0.2734</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.266</v>
+        <v>0.8132</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>0.8132</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2396</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.5161</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1667</v>
+        <v>0.5837</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.651</v>
+        <v>0.6132</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2519</v>
+        <v>0.9928</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3991</v>
+        <v>-0.3796</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4801</v>
+        <v>2.0462</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9529</v>
+        <v>1.2405</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5272</v>
+        <v>0.8058</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1311</v>
+        <v>-1.433</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2048</v>
+        <v>-0.2477</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9263</v>
+        <v>-1.1853</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1984</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2035</v>
+        <v>1.0415</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5611</v>
+        <v>0.3458</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3576</v>
+        <v>0.6956</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8132</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X19" t="n">
-        <v>0.8132</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.184</v>
+        <v>-0.8796</v>
       </c>
       <c r="E20" t="n">
         <v>-0.3369</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8472</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7756</v>
@@ -2014,13 +2014,13 @@
         <v>1.1903</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.07480000000000001</v>
+        <v>0.2296</v>
       </c>
       <c r="T20" t="n">
         <v>0.1814</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2562</v>
+        <v>0.0481</v>
       </c>
       <c r="V20" t="n">
         <v>-0.532</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>H. MORRO BALERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6586</v>
+        <v>-1.5095</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3715</v>
+        <v>-0.9294</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2871</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5658</v>
+        <v>-0.9115</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8198</v>
+        <v>-0.0707</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2541</v>
+        <v>-0.8408</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3685</v>
+        <v>0.0229</v>
       </c>
       <c r="K21" t="n">
-        <v>0.121</v>
+        <v>0.0605</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2476</v>
+        <v>-0.0376</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.9343</v>
+        <v>-0.9344</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9408</v>
+        <v>-0.1312</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0065</v>
+        <v>-0.8032</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3887</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2284</v>
+        <v>-0.0028</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2438</v>
+        <v>0.0397</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0153</v>
+        <v>-0.0425</v>
       </c>
       <c r="V21" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. MORRO BALERA</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6676</v>
+        <v>-1.8346</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0314</v>
+        <v>-0.5756</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6362</v>
+        <v>-1.259</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9115</v>
+        <v>-0.5658</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0707</v>
+        <v>-1.8198</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8408</v>
+        <v>1.2541</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0229</v>
+        <v>1.3685</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0605</v>
+        <v>0.121</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0376</v>
+        <v>1.2476</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9344</v>
+        <v>-1.9343</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1312</v>
+        <v>-1.9408</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8032</v>
+        <v>0.0065</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5952</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.161</v>
+        <v>0.0524</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.0127</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.0675</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.0675</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3895</v>
+        <v>-5.1208</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.7339</v>
+        <v>-6.9379</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3444</v>
+        <v>1.8171</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1111</v>
@@ -2248,13 +2248,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.3628</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1758</v>
+        <v>-0.0282</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.391</v>
       </c>
       <c r="V23" t="n">
         <v>1.2065</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.5657</v>
+        <v>-6.6832</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0387</v>
+        <v>-5.3245</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.527</v>
+        <v>-1.3587</v>
       </c>
       <c r="G24" t="n">
         <v>-5.3997</v>
@@ -2326,13 +2326,13 @@
         <v>1.5871</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1064</v>
+        <v>-0.2238</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2469</v>
+        <v>-0.5327</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1405</v>
+        <v>0.3089</v>
       </c>
       <c r="V24" t="n">
         <v>-0.4645</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8231</v>
+        <v>-4.1431</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.0779</v>
+        <v>-5.078</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2546999999999999</v>
+        <v>0.9348000000000003</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.465900000000001</v>
+        <v>-5.465900000000002</v>
       </c>
       <c r="H25" t="n">
         <v>-6.7287</v>
@@ -2380,7 +2380,7 @@
         <v>9.002200000000002</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2057</v>
+        <v>3.205700000000001</v>
       </c>
       <c r="L25" t="n">
         <v>5.7967</v>
@@ -2404,13 +2404,13 @@
         <v>12.8951</v>
       </c>
       <c r="S25" t="n">
-        <v>2.352300000000001</v>
+        <v>3.0327</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2543</v>
+        <v>-0.2542999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>2.6067</v>
+        <v>3.2867</v>
       </c>
       <c r="V25" t="n">
         <v>4.2417</v>
